--- a/data/has_dash_records.xlsx
+++ b/data/has_dash_records.xlsx
@@ -1018,7 +1018,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>alkaline igneous rock</t>
+          <t>igneous rock</t>
         </is>
       </c>
     </row>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>alkaline igneous rock</t>
+          <t>igneous rock (inferred, low confidence)</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>alkaline igneous / carbonatite (inferred, medium confidence)</t>
+          <t>felsic igneous or sedimentary rock (inferred, low confidence)</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>alkaline igneous / carbonatite (inferred, medium confidence)</t>
+          <t>igneous-related hydrothermal rock (inferred, low confidence)</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>alkaline igneous rock</t>
+          <t>igneous rock</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>alkaline igneous rock</t>
+          <t>igneous rock (inferred, low confidence)</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>alkaline igneous rock</t>
+          <t>igneous rock</t>
         </is>
       </c>
     </row>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>alkaline igneous rock</t>
+          <t>igneous rock</t>
         </is>
       </c>
     </row>
@@ -4784,7 +4784,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>alkaline igneous rock</t>
+          <t>igneous rock (inferred, low confidence)</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>alkaline igneous rock</t>
+          <t>igneous rock (inferred, low confidence)</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>alkaline igneous rock</t>
+          <t>igneous rock</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>alkaline igneous rock</t>
+          <t>igneous rock</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>alkaline igneous rock</t>
+          <t>igneous rock (inferred, low confidence)</t>
         </is>
       </c>
     </row>
